--- a/nr-test-examples/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/nr-test-examples/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-13T08:37:28+00:00</t>
+    <t>2025-08-19T10:24:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-test-examples/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/nr-test-examples/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-19T10:24:15+00:00</t>
+    <t>2025-08-20T12:47:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-test-examples/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/nr-test-examples/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-20T12:47:24+00:00</t>
+    <t>2025-08-21T07:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-test-examples/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/nr-test-examples/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-21T07:33:49+00:00</t>
+    <t>2025-08-21T08:16:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-test-examples/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/nr-test-examples/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-21T08:16:49+00:00</t>
+    <t>2025-08-21T09:25:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-test-examples/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/nr-test-examples/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-21T09:25:17+00:00</t>
+    <t>2025-08-21T15:51:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-test-examples/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/nr-test-examples/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-21T15:51:37+00:00</t>
+    <t>2025-08-21T16:15:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-test-examples/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/nr-test-examples/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-21T16:15:18+00:00</t>
+    <t>2025-08-22T07:28:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-test-examples/ig/StructureDefinition-fr-core-associated-entity.xlsx
+++ b/nr-test-examples/ig/StructureDefinition-fr-core-associated-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T07:28:23+00:00</t>
+    <t>2025-08-22T07:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
